--- a/test_run/AnhDThe187386/TC1/GradeDetail.xlsx
+++ b/test_run/AnhDThe187386/TC1/GradeDetail.xlsx
@@ -158,16 +158,64 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN_RECEIVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESTABLISHED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E..8..@.@.M.............K6J3.&lt;*......,.........I...BS001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E..4.,@.@.j..............&lt;*.K6J7.....(.........I...I</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E....-@.@.i..............&lt;*.K6J7...............m...I{"StudentId":"S001","Name":"John.Smith","Major":"Computer.Science","Year":3,"GPA":3.5,"Status":"success","Message":"Student.information.retrieved.successfully"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E..4..@.@.M.............K6J7.&lt;+'.....(.........m...m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN_WAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E..4..@.@.j..............&lt;+'K6J7.....(.........m...m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E..4..@.@.M.............K6J7.&lt;+(.....(.............m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E..4./@.@.j..............&lt;+(K6J8.....(..............</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -194,7 +242,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -203,7 +251,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -226,7 +279,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -236,8 +289,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -247,6 +303,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -873,11 +933,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R3"/>
+  <x:dimension ref="A1:R11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -886,11 +946,11 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.139196" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="191.996339" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="16.424911" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="14.424911" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="14.139196" style="0" customWidth="1"/>
@@ -984,25 +1044,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1040,28 +1100,476 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P3" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>42700</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:18">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:18">
+      <x:c r="A5" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="P5" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R5" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:18">
+      <x:c r="A6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="P6" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="R6" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:18">
+      <x:c r="A7" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="R7" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:18">
+      <x:c r="A8" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="P8" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="Q8" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="P9" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="R9" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:18">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="P10" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R10" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:18">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>42700</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
